--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486387_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486387_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.715400000000001</v>
+        <v>8.447699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9439</v>
+        <v>7.5221</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7715</v>
+        <v>0.9256</v>
       </c>
       <c r="G2" t="n">
         <v>6.9615</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8839</v>
+        <v>0.6162</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6682</v>
+        <v>0.2464</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2157</v>
+        <v>0.3698</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3057</v>
+        <v>8.347300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.82</v>
+        <v>4.4473</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4857</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
         <v>3.6362</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1045</v>
+        <v>1.1461</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6044</v>
+        <v>0.0228</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7089</v>
+        <v>1.1233</v>
       </c>
       <c r="V3" t="n">
         <v>2.2599</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2127</v>
+        <v>4.5402</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7796</v>
+        <v>2.8913</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4331</v>
+        <v>1.6489</v>
       </c>
       <c r="G4" t="n">
         <v>3.9128</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2123</v>
+        <v>0.5399</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.536</v>
+        <v>-0.4242</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7483</v>
+        <v>0.9641</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.559</v>
+        <v>4.1541</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9184</v>
+        <v>3.2285</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3594</v>
+        <v>0.9256</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7146</v>
+        <v>1.7152</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4289</v>
+        <v>-0.6722</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1435</v>
+        <v>2.3874</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7284</v>
+        <v>3.117</v>
       </c>
       <c r="K5" t="n">
-        <v>0.949</v>
+        <v>-0.2888</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7794</v>
+        <v>3.4058</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0138</v>
+        <v>-1.4018</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3779</v>
+        <v>-0.3834</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6359</v>
+        <v>-1.0184</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0256</v>
+        <v>0.2436</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0601</v>
+        <v>-0.1262</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0857</v>
+        <v>0.3698</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3727</v>
+        <v>3.6198</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0134</v>
+        <v>0.6664</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3593</v>
+        <v>2.9534</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8536</v>
+        <v>3.8629</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3747</v>
+        <v>2.2445</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5212</v>
+        <v>1.6184</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4689</v>
+        <v>4.3532</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3542</v>
+        <v>2.2478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1147</v>
+        <v>2.1053</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6153</v>
+        <v>-0.4902</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9794</v>
+        <v>-0.0033</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6359</v>
+        <v>-0.4869</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5225</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0411</v>
+        <v>0.5399</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.411</v>
+        <v>-0.4242</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4521</v>
+        <v>0.9641</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9554</v>
+        <v>0.7395</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3042</v>
+        <v>3.5461</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5327</v>
+        <v>3.1251</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7715</v>
+        <v>0.4209</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7152</v>
+        <v>0.8536</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6722</v>
+        <v>1.3747</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3874</v>
+        <v>-0.5212</v>
       </c>
       <c r="J7" t="n">
-        <v>3.117</v>
+        <v>2.4689</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2888</v>
+        <v>2.3542</v>
       </c>
       <c r="L7" t="n">
-        <v>3.4058</v>
+        <v>0.1147</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4018</v>
+        <v>-1.6153</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3834</v>
+        <v>-0.9794</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0184</v>
+        <v>-0.6359</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6063</v>
+        <v>0.2145</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.2992</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2157</v>
+        <v>0.5137</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3252</v>
+        <v>0.9554</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3252</v>
+        <v>0.9554</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2923</v>
+        <v>3.4395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5546</v>
+        <v>3.5832</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7376</v>
+        <v>-0.1437</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8629</v>
+        <v>0.7146</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2445</v>
+        <v>-0.4289</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6184</v>
+        <v>1.1435</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3532</v>
+        <v>2.7284</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2478</v>
+        <v>0.949</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1053</v>
+        <v>1.7794</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4902</v>
+        <v>-2.0138</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0033</v>
+        <v>-1.3779</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4869</v>
+        <v>-0.6359</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2123</v>
+        <v>-0.1451</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.536</v>
+        <v>-0.2752</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7483</v>
+        <v>0.1301</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7519</v>
+        <v>2.5038</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3859</v>
+        <v>-0.3871</v>
       </c>
       <c r="F9" t="n">
-        <v>0.366</v>
+        <v>2.891</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1075</v>
+        <v>-0.5999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.6081</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8718</v>
+        <v>-1.208</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5244</v>
+        <v>-1.5712</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9307</v>
+        <v>-0.2341</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5937</v>
+        <v>-1.3371</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4169</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0486</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4654</v>
+        <v>0.1291</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5138</v>
+        <v>1.1038</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4711</v>
+        <v>0.0541</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0428</v>
+        <v>1.0497</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5287</v>
+        <v>2.4898</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3006</v>
+        <v>1.9389</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8293</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5999</v>
+        <v>0.1075</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6081</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.208</v>
+        <v>-0.8718</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5712</v>
+        <v>1.5244</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2341</v>
+        <v>0.9307</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3371</v>
+        <v>0.5937</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9713000000000001</v>
+        <v>-1.4169</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.0486</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1291</v>
+        <v>-1.4654</v>
       </c>
       <c r="P10" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1286</v>
+        <v>0.2518</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1406</v>
+        <v>0.024</v>
       </c>
       <c r="U10" t="n">
-        <v>0.988</v>
+        <v>0.2277</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7133</v>
+        <v>-0.5523</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1668</v>
+        <v>-0.0983</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5465</v>
+        <v>-0.454</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0953</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0856</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.137</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4349</v>
+        <v>-1.5753</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.7365</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5614</v>
+        <v>-0.8389</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1253</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2331</v>
+        <v>1.0926</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2776</v>
+        <v>0.4146</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9555</v>
+        <v>0.678</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3252</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1491</v>
+        <v>-2.5306</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9163</v>
+        <v>-3.8045</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7672</v>
+        <v>1.274</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9266</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7551</v>
+        <v>0.3737</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8904</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6456</v>
+        <v>1.1524</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1952</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>35.74530000000001</v>
+        <v>36.4301</v>
       </c>
       <c r="E14" t="n">
-        <v>21.6913</v>
+        <v>22.3764</v>
       </c>
       <c r="F14" t="n">
-        <v>14.0539</v>
+        <v>14.0537</v>
       </c>
       <c r="G14" t="n">
         <v>16.0172</v>
@@ -1540,25 +1540,25 @@
         <v>8.700199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.787699999999999</v>
+        <v>-9.787700000000001</v>
       </c>
       <c r="R14" t="n">
         <v>18.4882</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3775</v>
+        <v>6.062600000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3192</v>
+        <v>-1.6343</v>
       </c>
       <c r="U14" t="n">
         <v>7.696800000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.649800000000001</v>
+        <v>5.6498</v>
       </c>
       <c r="W14" t="n">
-        <v>8.3209</v>
+        <v>8.320899999999998</v>
       </c>
       <c r="X14" t="n">
         <v>-2.6711</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3239</v>
+        <v>-0.2315</v>
       </c>
       <c r="E15" t="n">
         <v>0.7794</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1033</v>
+        <v>-1.0109</v>
       </c>
       <c r="G15" t="n">
         <v>0.5492</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5909</v>
+        <v>-0.4984</v>
       </c>
       <c r="T15" t="n">
         <v>-1.0274</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4366</v>
+        <v>0.529</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9347</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3089</v>
+        <v>-1.3706</v>
       </c>
       <c r="E16" t="n">
         <v>-0.3026</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0063</v>
+        <v>-1.0679</v>
       </c>
       <c r="G16" t="n">
         <v>0.5425</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5686</v>
+        <v>-0.6303</v>
       </c>
       <c r="T16" t="n">
         <v>-1.0959</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5273</v>
+        <v>0.4656</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1952</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0222</v>
+        <v>-1.5688</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1441</v>
+        <v>0.4794</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1663</v>
+        <v>-2.0481</v>
       </c>
       <c r="G17" t="n">
         <v>0.5759</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6851</v>
+        <v>-0.2316</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0684</v>
+        <v>0.1866</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3904</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8079</v>
+        <v>-2.0231</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8564</v>
+        <v>1.9681</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.6642</v>
+        <v>-3.9912</v>
       </c>
       <c r="G18" t="n">
         <v>1.8228</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4556</v>
+        <v>-0.6708</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5754</v>
+        <v>-1.4637</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1198</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5649999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2661</v>
+        <v>-3.1594</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2135</v>
+        <v>-0.1017</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.0526</v>
+        <v>-3.0577</v>
       </c>
       <c r="G19" t="n">
         <v>-4.2248</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6063</v>
+        <v>-0.4996</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9589</v>
+        <v>-0.8472</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3527</v>
+        <v>0.3476</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6822</v>
+        <v>-3.7669</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5378</v>
+        <v>-3.3143</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1443</v>
+        <v>-0.4526</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2796</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1851</v>
+        <v>-0.2698</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6369</v>
+        <v>0.3287</v>
       </c>
       <c r="V20" t="n">
         <v>-1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8014</v>
+        <v>-3.9517</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1673</v>
+        <v>-2.5026</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.634</v>
+        <v>-1.4491</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3887</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0224</v>
+        <v>-0.128</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1971</v>
+        <v>-0.1382</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1747</v>
+        <v>0.0102</v>
       </c>
       <c r="V21" t="n">
         <v>-1.695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9755</v>
+        <v>-5.3146</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.5437</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.8788</v>
+        <v>-4.7709</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6849</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0994</v>
+        <v>-0.2397</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4879</v>
+        <v>-0.9349</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5873</v>
+        <v>0.6952</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2599</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4349</v>
+        <v>-6.7137</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2801</v>
+        <v>-7.0121</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1548</v>
+        <v>0.2984</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.5068</v>
+        <v>-3.4229</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6795</v>
+        <v>-0.5414</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.8273</v>
+        <v>-2.8814</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2936</v>
+        <v>-3.002</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2497</v>
+        <v>-0.6721</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0439</v>
+        <v>-2.33</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.2132</v>
+        <v>-0.4208</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4298</v>
+        <v>0.1306</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7834</v>
+        <v>-0.5514</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="R23" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1011</v>
+        <v>-0.8983</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4194</v>
+        <v>-0.5299</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3183</v>
+        <v>-0.3683</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1222</v>
+        <v>-6.8485</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2356</v>
+        <v>-3.5036</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1134</v>
+        <v>-3.3448</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4229</v>
+        <v>-6.5068</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5414</v>
+        <v>-2.6795</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.8814</v>
+        <v>-3.8273</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.002</v>
+        <v>-3.2936</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6721</v>
+        <v>-1.2497</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.33</v>
+        <v>-2.0439</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4208</v>
+        <v>-3.2132</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1306</v>
+        <v>-1.4298</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5514</v>
+        <v>-1.7834</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4801</v>
+        <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3067</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.6429</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5533</v>
+        <v>0.1283</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-35.7452</v>
+        <v>-34.9488</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.0536</v>
+        <v>-14.0537</v>
       </c>
       <c r="F25" t="n">
-        <v>-21.6912</v>
+        <v>-20.8948</v>
       </c>
       <c r="G25" t="n">
         <v>-16.0173</v>
@@ -2377,13 +2377,13 @@
         <v>-6.4825</v>
       </c>
       <c r="J25" t="n">
-        <v>9.4602</v>
+        <v>9.460200000000002</v>
       </c>
       <c r="K25" t="n">
         <v>1.933500000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>7.5266</v>
+        <v>7.526599999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-25.4775</v>
@@ -2404,13 +2404,13 @@
         <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.3776</v>
+        <v>-4.581099999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.696800000000001</v>
+        <v>-7.696700000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3193</v>
+        <v>3.115699999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-5.649800000000001</v>
